--- a/rules/CORE-000880/positive/01/data/unit-test-coreid-FB4006-positive.xlsx
+++ b/rules/CORE-000880/positive/01/data/unit-test-coreid-FB4006-positive.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1902,6 +1902,99 @@
       <c r="T16" s="5" t="inlineStr">
         <is>
           <t>PT5H</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>CDISC002</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Albumin</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>ALBCAT1</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>g/dL</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>SERUM</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>METHOD-B</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>LB REASON2</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>SCREENING 1</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>2012-10-30T14:26</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>P2 days</t>
         </is>
       </c>
     </row>
